--- a/docs/video_manual/v1.6/exports/Report_City-wise_Freight.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_City-wise_Freight.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 18-10-2026 00:47 by Master Administrator</t>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>77</v>
@@ -581,13 +581,13 @@
         <v>261650</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1532.02</v>
+        <v>1713</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>19.9</v>
+        <v>22.25</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>127</v>
@@ -610,13 +610,13 @@
         <v>428700</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2456.02</v>
+        <v>2637</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>19.34</v>
+        <v>20.76</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>

--- a/docs/video_manual/v1.6/exports/Report_City-wise_Freight.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_City-wise_Freight.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
       <i val="1"/>
       <color rgb="005B6675"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -70,20 +75,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,52 +479,55 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
-        </is>
-      </c>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 14:47 by Master Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Depots</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Dispatched</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Boxes</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Calculated Freight</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Freight / Box</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Freight % of Sales</t>
         </is>
@@ -535,25 +544,25 @@
           <t>Bilaspur Depot (Demo)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>167050</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>924</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>18.48</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -568,54 +577,54 @@
           <t>Guma Depot (Demo), Kamal Vihar Depot (Demo)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>261650</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>1713</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>22.25</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.65</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>428700</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>2637</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>20.76</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="11" t="n">
         <v>0.62</v>
       </c>
     </row>
